--- a/production/watch-PRELIMINARY/Manufacturing/Assembly/ZSWatch-Watch-bom.xlsx
+++ b/production/watch-PRELIMINARY/Manufacturing/Assembly/ZSWatch-Watch-bom.xlsx
@@ -1040,7 +1040,7 @@
     <t>Created:</t>
   </si>
   <si>
-    <t>2026-10-21 09:39:06</t>
+    <t>2026-10-29 20:31:02</t>
   </si>
   <si>
     <t>KiCost® v1.1.21 + KiBot v1.9.1</t>
